--- a/pipeline/credit_rating/output/equity_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/equity_xhtn_20261027.xlsx
@@ -1541,12 +1541,12 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -1701,12 +1701,12 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="O36" t="n">
